--- a/www/download/IND.hours_worked.empe_hs.r.pc.rpPE.xlsx
+++ b/www/download/IND.hours_worked.empe_hs.r.pc.rpPE.xlsx
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -673,7 +678,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Austrália</t>
+          <t>32</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -683,84 +688,84 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>28.4</t>
+          <t>0.284043733074465</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>29.63</t>
+          <t>0.29630641524427</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>30.91</t>
+          <t>0.309062988716524</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>32.6</t>
+          <t>0.326005132445565</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>0.33872832971529</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>0.35415057198161</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>0.365081321216332</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>37.34</t>
+          <t>0.37343063315043</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>0.372804119651297</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>36.69</t>
+          <t>0.366926551257351</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>35.77</t>
+          <t>0.357664758889467</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>0.355848697211814</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>34.94</t>
+          <t>0.349388815167077</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>0.345337483033314</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>34.86</t>
+          <t>0.348632422905777</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Áustria</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -770,84 +775,84 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>23.46</t>
+          <t>0.234602813645671</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>0.236583751308925</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>23.73</t>
+          <t>0.237258153943366</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>24.49</t>
+          <t>0.244931312835306</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>0.289125421105195</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>29.76</t>
+          <t>0.297566333283515</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>29.7</t>
+          <t>0.297018474675315</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>30.46</t>
+          <t>0.30460997892329</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>30.26</t>
+          <t>0.30256312011383</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>0.355826996140506</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>34.27</t>
+          <t>0.342687477942264</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>0.338199112439914</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>0.339824427369156</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>32.8</t>
+          <t>0.327954827008148</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>0.348435910840834</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Bélgica</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -857,84 +862,84 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>28.52</t>
+          <t>0.285223364862848</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>29.16</t>
+          <t>0.291625399590196</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>0.297301535145453</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>30.49</t>
+          <t>0.304888959609711</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>30.74</t>
+          <t>0.307423361542342</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>31.05</t>
+          <t>0.310476575252776</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>31.17</t>
+          <t>0.311696585941848</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.32</t>
+          <t>0.31320548740358</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>30.99</t>
+          <t>0.309853912530507</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>31.96</t>
+          <t>0.319620908584757</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>31.91</t>
+          <t>0.319148448234882</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>31.82</t>
+          <t>0.318240658220735</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>32.24</t>
+          <t>0.322439784655136</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>35.42</t>
+          <t>0.354172629287933</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>35.78</t>
+          <t>0.357835761656807</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -944,84 +949,84 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>0.238398181075991</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.238066858392622</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>0.227747502565765</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.222195166027263</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0.227510176938149</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>0.236635290578604</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>0.237382087297179</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245302050306835</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275482376902733</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>0.28449733732479</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>0.295094001750916</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>0.298329438757012</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>0.301798731469841</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>0.316575687650561</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>0.330108019208722</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Brasil</t>
+          <t>33</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1031,84 +1036,84 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>29.21</t>
+          <t>0.292056439392701</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>29.5</t>
+          <t>0.294981329616625</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>29.84</t>
+          <t>0.29844484845715</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>30.59</t>
+          <t>0.305945657340006</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>30.88</t>
+          <t>0.308831226348176</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>31.39</t>
+          <t>0.313928835402701</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>31.44</t>
+          <t>0.314447190346627</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.49</t>
+          <t>0.314863050067905</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>31.14</t>
+          <t>0.311350279163561</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>31.53</t>
+          <t>0.31534195751525</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>31.51</t>
+          <t>0.315071987973295</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>32.42</t>
+          <t>0.324193155986775</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>32.87</t>
+          <t>0.328657418071521</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>33.48</t>
+          <t>0.334771896943119</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>0.346902943397423</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Canadá</t>
+          <t>34</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1118,84 +1123,84 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>26.58</t>
+          <t>0.265773108202805</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>27.02</t>
+          <t>0.27021346934453</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.66</t>
+          <t>0.276631343123594</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>28.82</t>
+          <t>0.288230597249128</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>28.61</t>
+          <t>0.286147535847147</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>29.73</t>
+          <t>0.297305022306055</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>30.68</t>
+          <t>0.306780924485413</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.21</t>
+          <t>0.312147083736856</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>31.64</t>
+          <t>0.316357000290611</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>32.11</t>
+          <t>0.321091586826374</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>33.29</t>
+          <t>0.332946934356065</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>34.46</t>
+          <t>0.344578699900339</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>35.32</t>
+          <t>0.353152120635281</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>34.8</t>
+          <t>0.348010817026354</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>36.64</t>
+          <t>0.366385160634606</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>China</t>
+          <t>35</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1205,84 +1210,84 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11.81</t>
+          <t>0.118129490462409</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>12.43</t>
+          <t>0.124270444161783</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13.05</t>
+          <t>0.130528293910002</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>13.87</t>
+          <t>0.138662899527161</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>14.49</t>
+          <t>0.144891816264447</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>15.26</t>
+          <t>0.15264954695307</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>15.84</t>
+          <t>0.158420917047524</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>16.46</t>
+          <t>0.164595191154716</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>17.6</t>
+          <t>0.176030431062496</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>18.56</t>
+          <t>0.185643360754725</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>20.7</t>
+          <t>0.206955023025718</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>22.65</t>
+          <t>0.226486029759758</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>21.53</t>
+          <t>0.215311687743926</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>22.5</t>
+          <t>0.224983211771094</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>0.227280432594078</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chipre</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1292,84 +1297,84 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>53.42</t>
+          <t>0.534188139336053</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>53.2</t>
+          <t>0.532011315873177</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>52.33</t>
+          <t>0.523302522577204</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>51.73</t>
+          <t>0.517250438282201</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>51.18</t>
+          <t>0.511809080747415</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>52.39</t>
+          <t>0.523897577386329</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>52.84</t>
+          <t>0.528373940845939</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>53.8</t>
+          <t>0.538035222905255</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>53.44</t>
+          <t>0.534350545187074</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>52.72</t>
+          <t>0.527190060394804</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>0.506043879902198</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>50.28</t>
+          <t>0.502750800440531</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>51.92</t>
+          <t>0.519150926758474</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>52.25</t>
+          <t>0.52249179233009</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>53.29</t>
+          <t>0.532869140480181</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>República Tcheca</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1379,84 +1384,84 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>19.57</t>
+          <t>0.195738153131984</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>19.79</t>
+          <t>0.197941792217399</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>19.95</t>
+          <t>0.199507028388376</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>0.202529044072281</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>0.206853922159065</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>21.27</t>
+          <t>0.212716340419057</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>21.6</t>
+          <t>0.216030604087627</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>22.28</t>
+          <t>0.222782891550221</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>22.2</t>
+          <t>0.222030350730464</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>23.36</t>
+          <t>0.233551011836644</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>23.47</t>
+          <t>0.234749422729202</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>24.11</t>
+          <t>0.241074563390058</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>23.78</t>
+          <t>0.237762534062421</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>24.69</t>
+          <t>0.246858486399837</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>0.268177610740323</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Alemanha</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1466,84 +1471,84 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>37.41</t>
+          <t>0.374057211720549</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.85</t>
+          <t>0.378481268737137</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>38.25</t>
+          <t>0.382511103575928</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>0.403875532454147</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>40.25</t>
+          <t>0.40252489919004</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>40.65</t>
+          <t>0.406461498175901</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>0.412085786241713</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>41.96</t>
+          <t>0.419573700804437</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>0.43686872168981</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>44.46</t>
+          <t>0.444551144372013</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>44.02</t>
+          <t>0.440210459364758</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>43.11</t>
+          <t>0.43113361612827</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>41.94</t>
+          <t>0.419368987361779</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>42.42</t>
+          <t>0.42424920686823</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>0.444678871397695</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Dinamarca</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1553,84 +1558,84 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>37.11</t>
+          <t>0.371135744767938</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>38.36</t>
+          <t>0.38357033944765</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>39.47</t>
+          <t>0.394732549293486</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>0.409362289721991</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>41.5</t>
+          <t>0.414999200794754</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>41.91</t>
+          <t>0.419087038710207</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>42.84</t>
+          <t>0.428357563003439</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>43.77</t>
+          <t>0.437689560925577</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>47.74</t>
+          <t>0.47743418424337</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>48.27</t>
+          <t>0.482655130010994</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>49.76</t>
+          <t>0.497568952917515</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>0.502082718649866</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>47.4</t>
+          <t>0.474004819761633</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>49.96</t>
+          <t>0.499557535277039</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>50.93</t>
+          <t>0.509258512745328</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Espanha</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1640,84 +1645,84 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>50.22</t>
+          <t>0.502212188839657</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52.66</t>
+          <t>0.526594559913063</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>53.26</t>
+          <t>0.532620188756776</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>56.34</t>
+          <t>0.563416504507071</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>57.75</t>
+          <t>0.577467354823664</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>60.53</t>
+          <t>0.605268724936211</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>61.63</t>
+          <t>0.616308415893106</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>62.55</t>
+          <t>0.625489173903498</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>62.18</t>
+          <t>0.621783742025194</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>63.12</t>
+          <t>0.631171986416589</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>63.56</t>
+          <t>0.635649537039609</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>63.68</t>
+          <t>0.636768471379647</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>63.19</t>
+          <t>0.631919201015457</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>62.85</t>
+          <t>0.628543427804054</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>0.644977705921931</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Estônia</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1727,84 +1732,84 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>51.02</t>
+          <t>0.510194005469245</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>50.69</t>
+          <t>0.506897973279116</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>50.21</t>
+          <t>0.502096355779721</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>49.9</t>
+          <t>0.499023923491865</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>48.46</t>
+          <t>0.484580943973699</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>49.44</t>
+          <t>0.494418784456377</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>49.79</t>
+          <t>0.497882658559247</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>50.66</t>
+          <t>0.506571830216816</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>49.65</t>
+          <t>0.496531154436297</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>51.71</t>
+          <t>0.517111672447796</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>53.42</t>
+          <t>0.534229883919418</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>52.93</t>
+          <t>0.529341015069056</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>0.524405747894348</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>52.69</t>
+          <t>0.526859469726821</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>54.25</t>
+          <t>0.542488406709975</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Finlândia</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1814,84 +1819,84 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>51.67</t>
+          <t>0.516679052562779</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>52.51</t>
+          <t>0.525107835371396</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>52.95</t>
+          <t>0.529455403089147</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>53.47</t>
+          <t>0.534682944120706</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>53.67</t>
+          <t>0.536735308658135</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>53.89</t>
+          <t>0.538873192063711</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>54.14</t>
+          <t>0.541407308431005</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>54.43</t>
+          <t>0.544277727199811</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>54.3</t>
+          <t>0.542997967469293</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>0.549997061840417</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>54.82</t>
+          <t>0.548210379709188</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>54.72</t>
+          <t>0.547183096131396</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>54.86</t>
+          <t>0.548640341217876</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>54.99</t>
+          <t>0.549866790498685</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>0.572426672816675</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>França</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1901,84 +1906,84 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>0.394631843178548</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40.64</t>
+          <t>0.406424273924636</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>41.76</t>
+          <t>0.417567272256657</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>43.19</t>
+          <t>0.43192215911312</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>44.67</t>
+          <t>0.446741941605926</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>45.5</t>
+          <t>0.454978153042338</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>46.23</t>
+          <t>0.462332387466295</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>46.66</t>
+          <t>0.466564029721984</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>46.5</t>
+          <t>0.465005840304817</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>47.61</t>
+          <t>0.476069977369524</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>49.07</t>
+          <t>0.490675819588453</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>0.505975952643866</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>50.46</t>
+          <t>0.504591322015029</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>50.76</t>
+          <t>0.507608267506588</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>53.35</t>
+          <t>0.53354962942949</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Reino Unido</t>
+          <t>30</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1988,84 +1993,84 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>41.4</t>
+          <t>0.414042142524459</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41.39</t>
+          <t>0.413942841122809</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>42.9</t>
+          <t>0.429034845857683</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.32</t>
+          <t>0.453224205605764</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>47.17</t>
+          <t>0.47165999317663</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>49.42</t>
+          <t>0.49422325478289</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>50.4</t>
+          <t>0.504017758901097</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>51.4</t>
+          <t>0.514048000755015</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>50.52</t>
+          <t>0.505245281554234</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>49.72</t>
+          <t>0.497210036394539</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>50.11</t>
+          <t>0.50106322751836</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>51.14</t>
+          <t>0.511416453848888</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>53.06</t>
+          <t>0.530639002922982</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>52.7</t>
+          <t>0.526971340937653</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>53.34</t>
+          <t>0.533403199196317</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Grécia</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2075,84 +2080,84 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>36.41</t>
+          <t>0.364120019128725</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>0.371951890543951</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>37.7</t>
+          <t>0.377011312868589</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>38.55</t>
+          <t>0.385492739106996</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>36.84</t>
+          <t>0.368419376413065</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>0.381028449732194</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>37.77</t>
+          <t>0.377660463099106</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>38.56</t>
+          <t>0.385623774408109</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>0.384756997569524</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>40.34</t>
+          <t>0.403369306030845</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>39.71</t>
+          <t>0.397078483987444</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>0.424801081554011</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>42.77</t>
+          <t>0.427691045808806</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>42.63</t>
+          <t>0.426317676863096</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>43.14</t>
+          <t>0.431350493579465</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Hungria</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2162,84 +2167,84 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>0.260413920588253</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26.29</t>
+          <t>0.262933092542137</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>26.49</t>
+          <t>0.264866997080023</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>26.89</t>
+          <t>0.268896858663875</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>0.287573805664277</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>27.94</t>
+          <t>0.279410572954901</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>27.97</t>
+          <t>0.279652578062721</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>28.21</t>
+          <t>0.282085772447841</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>29.09</t>
+          <t>0.290936560998481</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>31.42</t>
+          <t>0.314212894560748</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>32.21</t>
+          <t>0.322127152604479</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>32.57</t>
+          <t>0.325747420464897</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>0.321225903235019</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>34.32</t>
+          <t>0.343158586003545</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>0.348858261760017</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Indonésia</t>
+          <t>39</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2249,84 +2254,84 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>0.163448625515185</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>17.42</t>
+          <t>0.174173666731475</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>16.98</t>
+          <t>0.169824818686202</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>19.27</t>
+          <t>0.192682391319338</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>19.85</t>
+          <t>0.198538714258504</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>22.47</t>
+          <t>0.224662752538644</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>22.76</t>
+          <t>0.227553748777633</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>22.64</t>
+          <t>0.226412505584005</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>20.98</t>
+          <t>0.209753643402478</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>0.227748108396249</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>23.43</t>
+          <t>0.234278388528367</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>24.02</t>
+          <t>0.240210766964621</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>23.85</t>
+          <t>0.238546251834537</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>23.5</t>
+          <t>0.234956578962926</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>0.237391701581935</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Índia</t>
+          <t>38</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2336,84 +2341,84 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>28.76</t>
+          <t>0.287574730278196</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>0.291818090657168</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>29.59</t>
+          <t>0.295885776350188</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>30.27</t>
+          <t>0.302730361537393</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>30.58</t>
+          <t>0.305783499312606</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>32.65</t>
+          <t>0.326498463449756</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>34.28</t>
+          <t>0.34280659440456</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>35.85</t>
+          <t>0.358516762729589</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>36.9</t>
+          <t>0.369000710077315</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>0.384828271046484</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>0.38303912572535</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>38.16</t>
+          <t>0.381584818554321</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>37.61</t>
+          <t>0.376145206335676</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>37.28</t>
+          <t>0.372770946799532</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>37.57</t>
+          <t>0.375709448938946</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Irlanda</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2423,84 +2428,84 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>39.95</t>
+          <t>0.399497460678936</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>41.75</t>
+          <t>0.417526562400359</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>42.13</t>
+          <t>0.421305182345494</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>44.43</t>
+          <t>0.44425831591562</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>46.1</t>
+          <t>0.460988834339052</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>0.473238014016951</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>48.44</t>
+          <t>0.48443526795038</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>0.505912291809547</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>52.44</t>
+          <t>0.52443449691487</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>55.14</t>
+          <t>0.551368277759004</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>55.59</t>
+          <t>0.555910685311692</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>57.11</t>
+          <t>0.571065084545936</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>57.78</t>
+          <t>0.57784340424839</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>0.590012812057471</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>61.9</t>
+          <t>0.618993417958337</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Itália</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2510,84 +2515,84 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>18.89</t>
+          <t>0.188944575645842</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>0.197063584116023</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>20.58</t>
+          <t>0.205766943282411</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>21.7</t>
+          <t>0.216965366022052</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>23.21</t>
+          <t>0.232072316362728</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>23.59</t>
+          <t>0.235898101995575</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>24.64</t>
+          <t>0.246379530591052</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>25.57</t>
+          <t>0.255737688963193</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>25.96</t>
+          <t>0.259631735704018</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>24.3</t>
+          <t>0.243016693395062</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>26.42</t>
+          <t>0.264150973681238</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>27.84</t>
+          <t>0.278363074939943</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>28.41</t>
+          <t>0.284136293914563</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>30.51</t>
+          <t>0.305130941244118</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>29.88</t>
+          <t>0.298800930646178</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Japão</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2597,84 +2602,84 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>33.71</t>
+          <t>0.337065498109691</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>34.69</t>
+          <t>0.346933223690957</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>35.47</t>
+          <t>0.354699529306754</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>36.98</t>
+          <t>0.369785855954179</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>37.86</t>
+          <t>0.37862499004562</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>38.68</t>
+          <t>0.3867719414465</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>0.397458895979981</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>40.96</t>
+          <t>0.409567225612581</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>40.95</t>
+          <t>0.40946676846145</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>41.24</t>
+          <t>0.41240855468034</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>0.410323906721809</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>40.99</t>
+          <t>0.40987346388389</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>0.406010462454583</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>40.38</t>
+          <t>0.403814469180385</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>40.71</t>
+          <t>0.407081832021567</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Coreia do Sul</t>
+          <t>37</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2684,84 +2689,84 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>47.35</t>
+          <t>0.473469201617925</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>0.495064814955153</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>50.59</t>
+          <t>0.505870438029475</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>53.95</t>
+          <t>0.539542855064602</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>55.26</t>
+          <t>0.552562412836565</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>55.28</t>
+          <t>0.552817466936433</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>56.64</t>
+          <t>0.566367718743138</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>60.01</t>
+          <t>0.60005342766198</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>60.5</t>
+          <t>0.605014268700685</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>61.02</t>
+          <t>0.610244600657547</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>0.619966181194362</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>61.93</t>
+          <t>0.619324275333163</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>61.51</t>
+          <t>0.615125046686014</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>61.27</t>
+          <t>0.612661172125183</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>61.59</t>
+          <t>0.615910062779854</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Lituânia</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2771,84 +2776,84 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>44.33</t>
+          <t>0.443293040487766</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>44.01</t>
+          <t>0.44011394011716</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>43.5</t>
+          <t>0.435028528549326</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>43.16</t>
+          <t>0.431579171849232</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>41.85</t>
+          <t>0.418473428162359</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>42.56</t>
+          <t>0.425554961483175</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>42.8</t>
+          <t>0.42804749122567</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>43.69</t>
+          <t>0.436917122786728</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>45.71</t>
+          <t>0.457087834938123</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>45.63</t>
+          <t>0.456304958443269</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>0.46929694022081</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>47.24</t>
+          <t>0.472379654022888</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>48.84</t>
+          <t>0.488436427417749</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>49.51</t>
+          <t>0.495064173032602</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>51.32</t>
+          <t>0.513168041746021</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Luxemburgo</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2858,84 +2863,84 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>43.51</t>
+          <t>0.435136046240349</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>40.41</t>
+          <t>0.404105373074456</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>38.71</t>
+          <t>0.387076645352333</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>37.47</t>
+          <t>0.374708708809749</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>35.92</t>
+          <t>0.359208034150221</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>36.51</t>
+          <t>0.365084546034093</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>0.366958022344193</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>0.370141389919287</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>28.32</t>
+          <t>0.283205052780309</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>42.51</t>
+          <t>0.425128395557335</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>44.59</t>
+          <t>0.445880476622543</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>0.39936610991988</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>42.34</t>
+          <t>0.423424222601748</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>40.67</t>
+          <t>0.406734097815402</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>49.77</t>
+          <t>0.497746025611862</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Letônia</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2945,84 +2950,84 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>0.395881757592248</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>39.27</t>
+          <t>0.392701930774458</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>38.72</t>
+          <t>0.387196866592603</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>38.38</t>
+          <t>0.383752164184667</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>37.2</t>
+          <t>0.372029165575177</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>37.97</t>
+          <t>0.37965514670144</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>38.2</t>
+          <t>0.382023897921697</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>0.38995113519108</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>0.36248648614206</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>39.46</t>
+          <t>0.394643263521509</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.370376819115011</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>37.98</t>
+          <t>0.379797083413979</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>40.32</t>
+          <t>0.403231569113578</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>0.441670167878609</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>43.95</t>
+          <t>0.439527751059664</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>México</t>
+          <t>40</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3032,84 +3037,84 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>0.364218245480781</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>36.15</t>
+          <t>0.36147496659137</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>35.6</t>
+          <t>0.356047527970788</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>36.38</t>
+          <t>0.363824516776902</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>36.36</t>
+          <t>0.363622295841404</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.370352712293457</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>36.71</t>
+          <t>0.36710733171447</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>36.52</t>
+          <t>0.365249810902513</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>35.93</t>
+          <t>0.359279913804627</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>35.74</t>
+          <t>0.357415745288753</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>35.37</t>
+          <t>0.353735941633337</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>34.36</t>
+          <t>0.343638587392638</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>33.87</t>
+          <t>0.338700795606482</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>33.57</t>
+          <t>0.335710159256983</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>33.88</t>
+          <t>0.338842353151659</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>22</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3119,84 +3124,84 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>0.238398181075991</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.238066858392622</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>0.227747502565765</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.222195166027263</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0.227510176938149</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>0.236635290578604</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>0.237382087297179</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245302050306835</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275482376902733</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>0.28449733732479</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>0.295094001750916</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>0.298329438757012</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>0.301798731469841</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>0.316575687650561</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>0.330108019208722</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Países Baixos</t>
+          <t>23</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3206,84 +3211,84 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>0.328809117239678</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>35.31</t>
+          <t>0.353068874863352</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>38.66</t>
+          <t>0.386595701395803</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>38.7</t>
+          <t>0.387038626647071</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>42.62</t>
+          <t>0.42617102096517</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>41.3</t>
+          <t>0.413025535935406</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>40.26</t>
+          <t>0.402617816145475</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>42.81</t>
+          <t>0.428133194133248</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>46.25</t>
+          <t>0.462542957892255</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>49.02</t>
+          <t>0.490238876319509</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>49.32</t>
+          <t>0.493220734456112</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>48.87</t>
+          <t>0.488654390485614</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>0.479971167281212</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>49.38</t>
+          <t>0.4937516558108</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>50.53</t>
+          <t>0.505312437965241</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Polônia</t>
+          <t>24</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -3293,84 +3298,84 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>22.99</t>
+          <t>0.229946680984898</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>23.24</t>
+          <t>0.232372539677916</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>23.41</t>
+          <t>0.234103501826759</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>23.75</t>
+          <t>0.237461283269928</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>23.8</t>
+          <t>0.238029187017944</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>24.04</t>
+          <t>0.24035119090802</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>25.98</t>
+          <t>0.259846805566291</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>27.47</t>
+          <t>0.274664411818863</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>29.86</t>
+          <t>0.298621892229648</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>32.96</t>
+          <t>0.32964380138817</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>34.29</t>
+          <t>0.342943902042983</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>35.25</t>
+          <t>0.352478046264778</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>35.57</t>
+          <t>0.355675678855799</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>35.95</t>
+          <t>0.359540796265443</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>38.64</t>
+          <t>0.38639430351597</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>25</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -3380,84 +3385,84 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>0.238398181075991</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.238066858392622</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>0.227747502565765</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.222195166027263</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0.227510176938149</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>0.236635290578604</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>0.237382087297179</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245302050306835</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275482376902733</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>0.28449733732479</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>0.295094001750916</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>0.298329438757012</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>0.301798731469841</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>0.316575687650561</t>
         </is>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>0.330108019208722</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Romênia</t>
+          <t>26</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -3467,84 +3472,84 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>23.84</t>
+          <t>0.238398181075991</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>23.81</t>
+          <t>0.238066858392622</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>22.77</t>
+          <t>0.227747502565765</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>0.222195166027263</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>22.75</t>
+          <t>0.227510176938149</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>23.66</t>
+          <t>0.236635290578604</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>23.74</t>
+          <t>0.237382087297179</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>24.53</t>
+          <t>0.245302050306835</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>27.55</t>
+          <t>0.275482376902733</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>28.45</t>
+          <t>0.28449733732479</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>29.51</t>
+          <t>0.295094001750916</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>29.83</t>
+          <t>0.298329438757012</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>30.18</t>
+          <t>0.301798731469841</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>31.66</t>
+          <t>0.316575687650561</t>
         </is>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>33.01</t>
+          <t>0.330108019208722</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Rússia</t>
+          <t>43</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3554,84 +3559,84 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>18.62</t>
+          <t>0.186189205710391</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>18.83</t>
+          <t>0.188273300426507</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>18.98</t>
+          <t>0.189759162992788</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>19.26</t>
+          <t>0.192639456044557</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>0.197085712200554</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>20.28</t>
+          <t>0.202813144213498</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>20.6</t>
+          <t>0.206031707997566</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>21.28</t>
+          <t>0.212801510068767</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>21.64</t>
+          <t>0.216394202215119</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>0.219585169959055</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>22.23</t>
+          <t>0.222311790407097</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>22.21</t>
+          <t>0.222079204426501</t>
         </is>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>21.96</t>
+          <t>0.21956996313441</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>0.218172980030862</t>
         </is>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>22.04</t>
+          <t>0.220413903743844</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Eslováquia</t>
+          <t>29</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3641,84 +3646,84 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>21.1</t>
+          <t>0.211008344088586</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>21.33</t>
+          <t>0.213348049175588</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>21.5</t>
+          <t>0.215008793712101</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>21.82</t>
+          <t>0.218212735533545</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20.59</t>
+          <t>0.205850520049375</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>20.9</t>
+          <t>0.209043856772959</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>21.45</t>
+          <t>0.21451022169284</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>21.32</t>
+          <t>0.213170852640502</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>22.39</t>
+          <t>0.223852337186016</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>0.231511884723507</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>25.26</t>
+          <t>0.252594461495765</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>26.23</t>
+          <t>0.262255344040652</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>25.85</t>
+          <t>0.258523238007071</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>25.81</t>
+          <t>0.25806113800367</t>
         </is>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>27.21</t>
+          <t>0.27214124745812</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Eslovênia</t>
+          <t>28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3728,84 +3733,84 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>28.15</t>
+          <t>0.281519967659908</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>0.284184185052441</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>28.62</t>
+          <t>0.286199757767536</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>29.03</t>
+          <t>0.290345267047633</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>30.08</t>
+          <t>0.300761039697868</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>32.27</t>
+          <t>0.322673721422432</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>27.07</t>
+          <t>0.270680253113914</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>0.299957637128807</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>33.08</t>
+          <t>0.330751338275378</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>0.347203820422465</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>35.46</t>
+          <t>0.354578604612584</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>36.7</t>
+          <t>0.367045813742857</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>36.89</t>
+          <t>0.368903749318359</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>0.381262358344905</t>
         </is>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>40.66</t>
+          <t>0.406646400301076</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Suécia</t>
+          <t>27</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3815,84 +3820,84 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>27.16</t>
+          <t>0.27156005152968</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27.62</t>
+          <t>0.276235586277053</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>28.42</t>
+          <t>0.284163274093895</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>29.34</t>
+          <t>0.29341208342311</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>0.30977630262991</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>0.338238262567957</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>34.81</t>
+          <t>0.348141695935354</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>35.74</t>
+          <t>0.357363249007057</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>35.94</t>
+          <t>0.359375158494355</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>37.19</t>
+          <t>0.371897958352377</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>0.388358476255639</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>40.47</t>
+          <t>0.404727527306802</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>40.6</t>
+          <t>0.405958670684372</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>42.25</t>
+          <t>0.422500298557268</t>
         </is>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>44.77</t>
+          <t>0.447698915248027</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Turquia</t>
+          <t>42</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3902,84 +3907,84 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>27.39</t>
+          <t>0.273898700828056</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>28.58</t>
+          <t>0.285769964997383</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>30.98</t>
+          <t>0.309845391376248</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>30.15</t>
+          <t>0.301531367431218</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>32.68</t>
+          <t>0.326808475062723</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>33.67</t>
+          <t>0.336730194410207</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>34.92</t>
+          <t>0.349216127324642</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>36.25</t>
+          <t>0.362487246496605</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>0.37098691215289</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>34.93</t>
+          <t>0.349253234789839</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>36.14</t>
+          <t>0.361418126726741</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>37.04</t>
+          <t>0.370422534957802</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>0.369968381806196</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>37.1</t>
+          <t>0.370995475807301</t>
         </is>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>38.02</t>
+          <t>0.380160206487896</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>China: Taiwan</t>
+          <t>36</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3989,84 +3994,84 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>45.9</t>
+          <t>0.459029956399588</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>46.93</t>
+          <t>0.469256517199509</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>47.92</t>
+          <t>0.479241307930404</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>49.31</t>
+          <t>0.493127225709394</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>50.13</t>
+          <t>0.501257492122647</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>51.15</t>
+          <t>0.511542684312693</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>51.63</t>
+          <t>0.516268094532225</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>52.06</t>
+          <t>0.520589129359029</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>52.15</t>
+          <t>0.521460885186818</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>53.01</t>
+          <t>0.530089547265963</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>53.84</t>
+          <t>0.538401054207687</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>0.552955835111875</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>54.66</t>
+          <t>0.546563579404155</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>55.76</t>
+          <t>0.55763643776773</t>
         </is>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>58.76</t>
+          <t>0.587616190317188</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Estados Unidos</t>
+          <t>31</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -4076,84 +4081,84 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>39.35</t>
+          <t>0.393489216019874</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>39.59</t>
+          <t>0.39589419121746</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>40.18</t>
+          <t>0.401802654738084</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>0.412918469448399</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>41.57</t>
+          <t>0.41565313224266</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>42.18</t>
+          <t>0.4218108069661</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>42.95</t>
+          <t>0.429478546868059</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>43.47</t>
+          <t>0.434693829156623</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>42.66</t>
+          <t>0.426579179382694</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>43.96</t>
+          <t>0.43962440659118</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>44.11</t>
+          <t>0.441134620449642</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>44.51</t>
+          <t>0.445080505094948</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.440749861628362</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>44.4</t>
+          <t>0.444027599471506</t>
         </is>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>45.77</t>
+          <t>0.457685565267283</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Resto do mundo</t>
+          <t>21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -4163,84 +4168,84 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>34.66</t>
+          <t>0.346645551889029</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>0.351850889481837</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>35.58</t>
+          <t>0.355803094605046</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>0.36444682230573</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>37.01</t>
+          <t>0.370134957044068</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>37.93</t>
+          <t>0.379251850644358</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>38.35</t>
+          <t>0.383504019275626</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>39.3</t>
+          <t>0.392991600060158</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>39.64</t>
+          <t>0.396402464540949</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>41.04</t>
+          <t>0.410375864096395</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>41.56</t>
+          <t>0.415584366178091</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>41.95</t>
+          <t>0.419540462527033</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>41.99</t>
+          <t>0.419886089700896</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>42.55</t>
+          <t>0.425499364608824</t>
         </is>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>44.07</t>
+          <t>0.440746337933719</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Mundo</t>
+          <t>46</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -4250,84 +4255,84 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>32.54</t>
+          <t>0.325401465102187</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>33.03</t>
+          <t>0.330325260421632</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>33.35</t>
+          <t>0.333515796341146</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>34.09</t>
+          <t>0.340928900159763</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>0.347024042821927</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>35.61</t>
+          <t>0.356073097297656</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>35.99</t>
+          <t>0.359915049160923</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>36.88</t>
+          <t>0.368832032476411</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>37.35</t>
+          <t>0.373540437929606</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>38.69</t>
+          <t>0.386879571334318</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>39.22</t>
+          <t>0.392194229568118</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>39.61</t>
+          <t>0.396097119053122</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>39.69</t>
+          <t>0.396896074917303</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
         <is>
-          <t>40.33</t>
+          <t>0.403268044363643</t>
         </is>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>41.77</t>
+          <t>0.417705616765273</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Croácia</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -4339,7 +4344,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Suíça</t>
+          <t>44</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -4351,7 +4356,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Noruega</t>
+          <t>41</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -4363,7 +4368,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Africa do Sul</t>
+          <t>45</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -4375,7 +4380,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Resto do mundo - Asia</t>
+          <t>47</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4387,7 +4392,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Resto do mundo - America</t>
+          <t>50</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4399,7 +4404,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Resto do mundo - Europa</t>
+          <t>48</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4411,7 +4416,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Resto do mundo - Africa</t>
+          <t>49</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4423,7 +4428,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Resto do mundo - Oriente Medio</t>
+          <t>51</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4470,6 +4475,11 @@
           <t>hours_worked.empe_hs.r.pc</t>
         </is>
       </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4504,6 +4514,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Petrovic</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpPE</t>
